--- a/data/scenario_summary.xlsx
+++ b/data/scenario_summary.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-16.18327017008382</v>
+        <v>-23.26181727909774</v>
       </c>
       <c r="F5" t="n">
         <v>-57.60216186307824</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-18.12923292446176</v>
+        <v>-19.2433255909228</v>
       </c>
       <c r="F29" t="n">
         <v>-58.21874751738557</v>
